--- a/grupos/5AEM - Estadisticos 20231.xlsx
+++ b/grupos/5AEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="93">
   <si>
     <t>Materia</t>
   </si>
@@ -191,21 +191,21 @@
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,52 +221,70 @@
     <t>ACEVEDO</t>
   </si>
   <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
     <t>ALDAHIR</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
+    <t>LUIS OMAR</t>
+  </si>
+  <si>
+    <t>CHARBEL</t>
+  </si>
+  <si>
+    <t>CANDIDO</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
   </si>
   <si>
     <t>CRISTHIAN</t>
@@ -275,19 +293,10 @@
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
+    <t>ROBERTO</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>LUIS OMAR</t>
-  </si>
-  <si>
-    <t>CHARBEL</t>
   </si>
 </sst>
 </file>
@@ -796,10 +805,10 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -811,28 +820,28 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -856,13 +865,13 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z4">
         <v>5</v>
@@ -874,7 +883,7 @@
         <v>6</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -903,25 +912,25 @@
         <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -951,13 +960,13 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z5">
         <v>6</v>
       </c>
       <c r="AA5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB5">
         <v>9</v>
@@ -992,25 +1001,25 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1037,7 +1046,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1052,7 +1061,7 @@
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1081,25 +1090,25 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1123,7 +1132,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1135,7 +1144,7 @@
         <v>9</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB7">
         <v>9</v>
@@ -1170,25 +1179,25 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1215,7 +1224,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1230,7 +1239,7 @@
         <v>10</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1259,25 +1268,25 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1301,25 +1310,25 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z9">
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1348,25 +1357,25 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1390,13 +1399,13 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <v>9</v>
@@ -1437,25 +1446,25 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1479,10 +1488,10 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1497,7 +1506,7 @@
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1526,25 +1535,25 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1568,10 +1577,10 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1615,25 +1624,25 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1657,10 +1666,10 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1669,7 +1678,7 @@
         <v>10</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>10</v>
@@ -1704,25 +1713,25 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1746,7 +1755,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1758,7 +1767,7 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>9</v>
@@ -1793,25 +1802,25 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1835,13 +1844,13 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z15">
         <v>9</v>
@@ -1882,25 +1891,25 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1930,19 +1939,19 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z16">
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1971,25 +1980,25 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2013,25 +2022,25 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>9</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2060,25 +2069,25 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2108,7 +2117,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z18">
         <v>9</v>
@@ -2149,25 +2158,25 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2194,16 +2203,16 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z19">
         <v>6</v>
       </c>
       <c r="AA19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>7</v>
@@ -2238,25 +2247,25 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2286,19 +2295,19 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z20">
         <v>8</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB20">
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2327,25 +2336,25 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2369,19 +2378,19 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>9</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB21">
         <v>10</v>
@@ -2416,25 +2425,25 @@
         <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2464,7 +2473,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>8</v>
@@ -2505,25 +2514,25 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2547,25 +2556,25 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2594,25 +2603,25 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2654,7 +2663,7 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2683,25 +2692,25 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2772,25 +2781,25 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2814,19 +2823,19 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>9</v>
@@ -2861,25 +2870,25 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2903,10 +2912,10 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2950,25 +2959,25 @@
         <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2992,7 +3001,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -3004,13 +3013,13 @@
         <v>6</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>8</v>
       </c>
       <c r="AC28">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3039,25 +3048,25 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3093,7 +3102,7 @@
         <v>9</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB29">
         <v>9</v>
@@ -3128,25 +3137,25 @@
         <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3176,19 +3185,19 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>6</v>
       </c>
       <c r="AA30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>7</v>
       </c>
       <c r="AC30">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3217,25 +3226,25 @@
         <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3259,19 +3268,19 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z31">
         <v>9</v>
       </c>
       <c r="AA31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB31">
         <v>9</v>
@@ -3306,25 +3315,25 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3360,13 +3369,13 @@
         <v>8</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB32">
         <v>10</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3395,25 +3404,25 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3443,7 +3452,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z33">
         <v>10</v>
@@ -3588,10 +3597,10 @@
         <v>85</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>90</v>
@@ -3603,16 +3612,16 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>90</v>
@@ -3624,16 +3633,16 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
         <v>90</v>
@@ -3645,7 +3654,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3674,13 +3683,13 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L5">
         <v>85</v>
@@ -3695,13 +3704,13 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S5">
         <v>85</v>
@@ -3742,7 +3751,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3763,7 +3772,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3810,13 +3819,13 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3831,13 +3840,13 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4082,34 +4091,34 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
+        <v>95</v>
+      </c>
+      <c r="L11">
+        <v>100</v>
+      </c>
+      <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
+        <v>100</v>
+      </c>
+      <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
         <v>90</v>
       </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
-      <c r="M11">
-        <v>100</v>
-      </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
-        <v>100</v>
-      </c>
-      <c r="P11">
-        <v>100</v>
-      </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -4150,19 +4159,19 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -4171,19 +4180,19 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -4230,7 +4239,7 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N13">
         <v>100</v>
@@ -4251,7 +4260,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -4286,7 +4295,7 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -4307,7 +4316,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4428,13 +4437,13 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L16">
         <v>90</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N16">
         <v>100</v>
@@ -4449,13 +4458,13 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S16">
         <v>90</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -4490,19 +4499,19 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L17">
         <v>90</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N17">
         <v>100</v>
@@ -4511,19 +4520,19 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S17">
         <v>90</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -4558,7 +4567,7 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -4570,7 +4579,7 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N18">
         <v>100</v>
@@ -4579,7 +4588,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4591,7 +4600,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -4626,19 +4635,19 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="L19">
         <v>70</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -4647,19 +4656,19 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="S19">
         <v>70</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -4700,13 +4709,13 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="L20">
         <v>85</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N20">
         <v>100</v>
@@ -4721,13 +4730,13 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="S20">
         <v>85</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U20">
         <v>100</v>
@@ -4830,19 +4839,19 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L22">
         <v>95</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N22">
         <v>100</v>
@@ -4851,19 +4860,19 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="S22">
         <v>95</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -4910,7 +4919,7 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -4931,7 +4940,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -4966,19 +4975,19 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L24">
         <v>70</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N24">
         <v>100</v>
@@ -4987,19 +4996,19 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="S24">
         <v>70</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -5034,19 +5043,19 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L25">
         <v>80</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N25">
         <v>100</v>
@@ -5055,19 +5064,19 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S25">
         <v>80</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -5102,19 +5111,19 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J26">
         <v>100</v>
       </c>
       <c r="K26">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -5123,19 +5132,19 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="S26">
         <v>100</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -5176,7 +5185,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -5197,7 +5206,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -5250,7 +5259,7 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -5271,7 +5280,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -5306,19 +5315,19 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N29">
         <v>100</v>
@@ -5327,19 +5336,19 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="S29">
         <v>100</v>
       </c>
       <c r="T29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -5374,19 +5383,19 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J30">
         <v>100</v>
       </c>
       <c r="K30">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="L30">
         <v>75</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N30">
         <v>100</v>
@@ -5395,19 +5404,19 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="S30">
         <v>75</v>
       </c>
       <c r="T30">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U30">
         <v>100</v>
@@ -5442,7 +5451,7 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J31">
         <v>100</v>
@@ -5463,7 +5472,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5683,25 +5692,25 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>76.7</v>
+        <v>80</v>
       </c>
       <c r="G2" s="2">
         <v>20</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5727,7 +5736,7 @@
         <v>16.7</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5738,7 +5747,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5759,7 +5768,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5770,7 +5779,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -5779,30 +5788,30 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="G5" s="2">
         <v>6.7</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -5811,19 +5820,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="G6" s="2">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5834,7 +5843,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -5855,7 +5864,7 @@
         <v>3.3</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5866,7 +5875,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>61</v>
@@ -5875,25 +5884,25 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5903,7 +5912,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5930,66 +5939,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920001</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920001</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5997,7 +5946,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6029,22 +5978,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920153</v>
+        <v>21330051920001</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6052,22 +6001,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920153</v>
+        <v>21330051920001</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6075,22 +6024,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920164</v>
+        <v>21330051920167</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6098,22 +6047,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920164</v>
+        <v>21330051920167</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6121,16 +6070,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920176</v>
+        <v>21330051920169</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -6144,22 +6093,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920176</v>
+        <v>21330051920169</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6167,16 +6116,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920069</v>
+        <v>21330051920176</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -6190,16 +6139,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920069</v>
+        <v>21330051920176</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -6213,16 +6162,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920166</v>
+        <v>20330051920069</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -6236,22 +6185,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920167</v>
+        <v>20330051920069</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
         <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6259,24 +6208,93 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920169</v>
+        <v>21330051920153</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
         <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920164</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920165</v>
+      </c>
+      <c r="B14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920166</v>
+      </c>
+      <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
         <v>56</v>
       </c>
-      <c r="G12">
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEM - Estadisticos 20231.xlsx
+++ b/grupos/5AEM - Estadisticos 20231.xlsx
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -927,7 +927,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>8</v>
@@ -969,7 +969,7 @@
         <v>7</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>8</v>
@@ -1016,7 +1016,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -1105,7 +1105,7 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>8</v>
@@ -1147,7 +1147,7 @@
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>8</v>
@@ -1194,7 +1194,7 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>9</v>
@@ -1283,7 +1283,7 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>9</v>
@@ -1372,7 +1372,7 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>8</v>
@@ -1550,7 +1550,7 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>9</v>
@@ -1592,7 +1592,7 @@
         <v>9</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>9</v>
@@ -1639,7 +1639,7 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>8</v>
@@ -1728,7 +1728,7 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>9</v>
@@ -1770,7 +1770,7 @@
         <v>9</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>10</v>
@@ -1817,7 +1817,7 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>9</v>
@@ -1859,7 +1859,7 @@
         <v>9</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>9</v>
@@ -1906,7 +1906,7 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
         <v>8</v>
@@ -1995,7 +1995,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>8</v>
@@ -2037,7 +2037,7 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC17">
         <v>7</v>
@@ -2084,7 +2084,7 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>8</v>
@@ -2173,7 +2173,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>8</v>
@@ -2262,7 +2262,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>5</v>
@@ -2351,7 +2351,7 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>8</v>
@@ -2393,7 +2393,7 @@
         <v>10</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>8</v>
@@ -2440,7 +2440,7 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>8</v>
@@ -2482,7 +2482,7 @@
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC22">
         <v>9</v>
@@ -2529,7 +2529,7 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>9</v>
@@ -2618,7 +2618,7 @@
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>9</v>
@@ -2707,7 +2707,7 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>9</v>
@@ -2749,7 +2749,7 @@
         <v>7</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>10</v>
@@ -2796,7 +2796,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>9</v>
@@ -2838,7 +2838,7 @@
         <v>9</v>
       </c>
       <c r="AB26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -2885,7 +2885,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>10</v>
@@ -2974,7 +2974,7 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>5</v>
@@ -3016,7 +3016,7 @@
         <v>8</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -3063,7 +3063,7 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>8</v>
@@ -3152,7 +3152,7 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>5</v>
@@ -3241,7 +3241,7 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>8</v>
@@ -3283,7 +3283,7 @@
         <v>10</v>
       </c>
       <c r="AB31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC31">
         <v>9</v>
@@ -3330,7 +3330,7 @@
         <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
         <v>8</v>
@@ -3372,7 +3372,7 @@
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC32">
         <v>9</v>
@@ -3419,7 +3419,7 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>9</v>
@@ -5832,7 +5832,7 @@
         <v>3.3</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/5AEM - Estadisticos 20231.xlsx
+++ b/grupos/5AEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="87">
   <si>
     <t>Materia</t>
   </si>
@@ -185,24 +185,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
@@ -236,12 +236,6 @@
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
     <t>MACARIO</t>
   </si>
   <si>
@@ -263,12 +257,6 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
     <t>NERI</t>
   </si>
   <si>
@@ -288,12 +276,6 @@
   </si>
   <si>
     <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
@@ -832,7 +814,7 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>9</v>
@@ -894,7 +876,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -921,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>9</v>
@@ -957,13 +939,13 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>9</v>
       </c>
       <c r="Z5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -1010,7 +992,7 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -1052,7 +1034,7 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA6">
         <v>10</v>
@@ -1099,7 +1081,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -1141,7 +1123,7 @@
         <v>7</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>9</v>
@@ -1188,7 +1170,7 @@
         <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -1230,7 +1212,7 @@
         <v>9</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -1366,7 +1348,7 @@
         <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1408,7 +1390,7 @@
         <v>8</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>9</v>
@@ -1455,7 +1437,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>9</v>
@@ -1497,7 +1479,7 @@
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -1544,7 +1526,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -1586,7 +1568,7 @@
         <v>9</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>9</v>
@@ -1722,7 +1704,7 @@
         <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1764,7 +1746,7 @@
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA14">
         <v>9</v>
@@ -1811,7 +1793,7 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>8</v>
@@ -1853,7 +1835,7 @@
         <v>8</v>
       </c>
       <c r="Z15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>9</v>
@@ -1873,7 +1855,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>7</v>
@@ -1900,7 +1882,7 @@
         <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>7</v>
@@ -1936,7 +1918,7 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1962,7 +1944,7 @@
         <v>8</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>7</v>
@@ -1989,7 +1971,7 @@
         <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -2025,7 +2007,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2078,7 +2060,7 @@
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>9</v>
@@ -2120,7 +2102,7 @@
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>9</v>
@@ -2167,7 +2149,7 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -2256,7 +2238,7 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -2298,7 +2280,7 @@
         <v>5</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>7</v>
@@ -2345,7 +2327,7 @@
         <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2387,7 +2369,7 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>10</v>
@@ -2434,7 +2416,7 @@
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>9</v>
@@ -2476,7 +2458,7 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2523,7 +2505,7 @@
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>7</v>
@@ -2565,7 +2547,7 @@
         <v>8</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>8</v>
@@ -2585,7 +2567,7 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>7</v>
@@ -2612,7 +2594,7 @@
         <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
@@ -2648,7 +2630,7 @@
         <v>7</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2674,7 +2656,7 @@
         <v>5</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -2701,7 +2683,7 @@
         <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -2737,13 +2719,13 @@
         <v>5</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>8</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -2790,7 +2772,7 @@
         <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>8</v>
@@ -2832,7 +2814,7 @@
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>9</v>
@@ -2879,7 +2861,7 @@
         <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -2921,7 +2903,7 @@
         <v>9</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA27">
         <v>10</v>
@@ -2968,7 +2950,7 @@
         <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>6</v>
@@ -3057,7 +3039,7 @@
         <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>7</v>
@@ -3099,7 +3081,7 @@
         <v>9</v>
       </c>
       <c r="Z29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA29">
         <v>9</v>
@@ -3119,7 +3101,7 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>9</v>
@@ -3146,7 +3128,7 @@
         <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M30">
         <v>6</v>
@@ -3182,13 +3164,13 @@
         <v>5</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>7</v>
       </c>
       <c r="Z30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA30">
         <v>8</v>
@@ -3235,7 +3217,7 @@
         <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>10</v>
@@ -3277,7 +3259,7 @@
         <v>9</v>
       </c>
       <c r="Z31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>10</v>
@@ -3324,7 +3306,7 @@
         <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>7</v>
@@ -3366,7 +3348,7 @@
         <v>9</v>
       </c>
       <c r="Z32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA32">
         <v>9</v>
@@ -3413,7 +3395,7 @@
         <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3455,7 +3437,7 @@
         <v>9</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA33">
         <v>10</v>
@@ -3624,7 +3606,7 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M4">
         <v>100</v>
@@ -3645,7 +3627,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="T4">
         <v>100</v>
@@ -3692,7 +3674,7 @@
         <v>97.5</v>
       </c>
       <c r="L5">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -3713,7 +3695,7 @@
         <v>97.5</v>
       </c>
       <c r="S5">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="T5">
         <v>100</v>
@@ -3896,7 +3878,7 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -3917,7 +3899,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -3964,7 +3946,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -3985,7 +3967,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -4032,7 +4014,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -4053,7 +4035,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -4100,7 +4082,7 @@
         <v>95</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -4121,7 +4103,7 @@
         <v>95</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -4236,7 +4218,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M13">
         <v>90</v>
@@ -4257,7 +4239,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T13">
         <v>90</v>
@@ -4576,7 +4558,7 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M18">
         <v>95</v>
@@ -4597,7 +4579,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T18">
         <v>95</v>
@@ -4644,7 +4626,7 @@
         <v>72.5</v>
       </c>
       <c r="L19">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M19">
         <v>90</v>
@@ -4665,7 +4647,7 @@
         <v>72.5</v>
       </c>
       <c r="S19">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="T19">
         <v>90</v>
@@ -4712,7 +4694,7 @@
         <v>72.5</v>
       </c>
       <c r="L20">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="M20">
         <v>90</v>
@@ -4733,7 +4715,7 @@
         <v>72.5</v>
       </c>
       <c r="S20">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="T20">
         <v>90</v>
@@ -4780,7 +4762,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -4801,7 +4783,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -4848,7 +4830,7 @@
         <v>92.5</v>
       </c>
       <c r="L22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M22">
         <v>95</v>
@@ -4869,7 +4851,7 @@
         <v>92.5</v>
       </c>
       <c r="S22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="T22">
         <v>95</v>
@@ -4916,7 +4898,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M23">
         <v>95</v>
@@ -4937,7 +4919,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T23">
         <v>95</v>
@@ -4984,7 +4966,7 @@
         <v>92.5</v>
       </c>
       <c r="L24">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M24">
         <v>90</v>
@@ -5005,7 +4987,7 @@
         <v>92.5</v>
       </c>
       <c r="S24">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="T24">
         <v>90</v>
@@ -5392,7 +5374,7 @@
         <v>82.5</v>
       </c>
       <c r="L30">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="M30">
         <v>90</v>
@@ -5413,7 +5395,7 @@
         <v>82.5</v>
       </c>
       <c r="S30">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="T30">
         <v>90</v>
@@ -5460,7 +5442,7 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -5481,7 +5463,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -5683,7 +5665,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -5692,19 +5674,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="G2" s="2">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5715,7 +5697,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -5779,7 +5761,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -5788,19 +5770,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="G5" s="2">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5811,7 +5793,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -5832,7 +5814,7 @@
         <v>3.3</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5843,7 +5825,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -5852,19 +5834,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5946,7 +5928,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5984,10 +5966,10 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -6007,16 +5989,16 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6030,16 +6012,16 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6053,10 +6035,10 @@
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -6076,16 +6058,16 @@
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6099,10 +6081,10 @@
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -6122,16 +6104,16 @@
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6145,16 +6127,16 @@
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6168,16 +6150,16 @@
         <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6191,16 +6173,16 @@
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6214,16 +6196,16 @@
         <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6231,70 +6213,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920164</v>
+        <v>21330051920166</v>
       </c>
       <c r="B13" t="s">
         <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
         <v>55</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920165</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920166</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEM - Estadisticos 20231.xlsx
+++ b/grupos/5AEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="75">
   <si>
     <t>Materia</t>
   </si>
@@ -185,24 +185,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
   </si>
   <si>
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
@@ -224,61 +224,25 @@
     <t>MAYO</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
     <t>ALDAHIR</t>
   </si>
   <si>
     <t>LUIS OMAR</t>
   </si>
   <si>
-    <t>CHARBEL</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
     <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
   </si>
 </sst>
 </file>
@@ -826,25 +790,25 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -853,19 +817,19 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB4">
         <v>6</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -915,43 +879,43 @@
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>9</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>7</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>8</v>
@@ -1004,25 +968,25 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1034,7 +998,7 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>10</v>
@@ -1093,43 +1057,43 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>7</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>8</v>
@@ -1182,25 +1146,25 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1212,7 +1176,7 @@
         <v>9</v>
       </c>
       <c r="Z8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -1221,7 +1185,7 @@
         <v>10</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1259,7 +1223,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1271,37 +1235,37 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>9</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA9">
         <v>9</v>
@@ -1360,25 +1324,25 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1393,7 +1357,7 @@
         <v>7</v>
       </c>
       <c r="AA10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>9</v>
@@ -1449,31 +1413,31 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1485,7 +1449,7 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>9</v>
@@ -1538,46 +1502,46 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="W12">
         <v>7</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>8</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1615,7 +1579,7 @@
         <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -1627,40 +1591,40 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>9</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>10</v>
@@ -1716,31 +1680,31 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1752,10 +1716,10 @@
         <v>9</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1805,31 +1769,31 @@
         <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>7</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1838,7 +1802,7 @@
         <v>8</v>
       </c>
       <c r="AA15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>8</v>
@@ -1894,28 +1858,28 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1924,13 +1888,13 @@
         <v>8</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>7</v>
@@ -1983,28 +1947,28 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -2016,7 +1980,7 @@
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>7</v>
@@ -2072,28 +2036,28 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2102,13 +2066,13 @@
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC18">
         <v>9</v>
@@ -2161,25 +2125,25 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2188,10 +2152,10 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>7</v>
@@ -2200,7 +2164,7 @@
         <v>7</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2250,43 +2214,43 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2339,31 +2303,31 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>8</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2428,25 +2392,25 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2458,10 +2422,10 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB22">
         <v>7</v>
@@ -2517,28 +2481,28 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>6</v>
@@ -2606,25 +2570,25 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2636,13 +2600,13 @@
         <v>7</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC24">
         <v>8</v>
@@ -2695,37 +2659,37 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>8</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -2784,25 +2748,25 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2820,7 +2784,7 @@
         <v>9</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -2873,25 +2837,25 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2906,7 +2870,7 @@
         <v>9</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB27">
         <v>8</v>
@@ -2962,46 +2926,46 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>7</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>9</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB28">
         <v>7</v>
       </c>
       <c r="AC28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3051,25 +3015,25 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -3140,46 +3104,46 @@
         <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>5</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3229,31 +3193,31 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>8</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -3265,7 +3229,7 @@
         <v>10</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC31">
         <v>9</v>
@@ -3318,25 +3282,25 @@
         <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -3351,7 +3315,7 @@
         <v>7</v>
       </c>
       <c r="AA32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB32">
         <v>9</v>
@@ -3407,31 +3371,31 @@
         <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>10</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3446,7 +3410,7 @@
         <v>10</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3618,7 +3582,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3627,7 +3591,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="T4">
         <v>100</v>
@@ -3686,19 +3650,19 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="S5">
-        <v>82.5</v>
+        <v>88.7</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U5">
         <v>100</v>
@@ -3754,7 +3718,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3822,19 +3786,19 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>87.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="S7">
         <v>100</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -3899,7 +3863,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -3946,7 +3910,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -3967,7 +3931,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>50</v>
+        <v>96.8</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -4035,7 +3999,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -4094,19 +4058,19 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="S11">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -4162,19 +4126,19 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="S12">
         <v>100</v>
       </c>
       <c r="T12">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -4218,7 +4182,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>90</v>
@@ -4239,10 +4203,10 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T13">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -4298,7 +4262,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4434,19 +4398,19 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="S16">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="T16">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -4502,19 +4466,19 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="S17">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="T17">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -4570,7 +4534,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4579,7 +4543,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="T18">
         <v>95</v>
@@ -4638,16 +4602,16 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>77.5</v>
+        <v>79.7</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>72.5</v>
+        <v>81.7</v>
       </c>
       <c r="S19">
-        <v>80</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="T19">
         <v>90</v>
@@ -4706,16 +4670,16 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R20">
-        <v>72.5</v>
+        <v>81.7</v>
       </c>
       <c r="S20">
-        <v>92.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="T20">
         <v>90</v>
@@ -4783,7 +4747,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -4842,19 +4806,19 @@
         <v>100</v>
       </c>
       <c r="P22">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>95</v>
       </c>
-      <c r="Q22">
-        <v>100</v>
-      </c>
-      <c r="R22">
-        <v>92.5</v>
-      </c>
       <c r="S22">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="T22">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -4919,10 +4883,10 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="T23">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -4978,19 +4942,19 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="S24">
-        <v>80</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="T24">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -5046,19 +5010,19 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="S25">
-        <v>80</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="T25">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -5114,19 +5078,19 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="S26">
         <v>100</v>
       </c>
       <c r="T26">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -5188,7 +5152,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -5262,7 +5226,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -5318,19 +5282,19 @@
         <v>100</v>
       </c>
       <c r="P29">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
         <v>95</v>
       </c>
-      <c r="Q29">
-        <v>100</v>
-      </c>
-      <c r="R29">
-        <v>92.5</v>
-      </c>
       <c r="S29">
         <v>100</v>
       </c>
       <c r="T29">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -5386,16 +5350,16 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>80</v>
+        <v>81.3</v>
       </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
-        <v>82.5</v>
+        <v>88.3</v>
       </c>
       <c r="S30">
-        <v>62.5</v>
+        <v>75.8</v>
       </c>
       <c r="T30">
         <v>90</v>
@@ -5454,7 +5418,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5463,7 +5427,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -5534,7 +5498,7 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -5665,7 +5629,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -5674,16 +5638,16 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>83.3</v>
+        <v>93.3</v>
       </c>
       <c r="G2" s="2">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="H2">
         <v>7.3</v>
@@ -5697,7 +5661,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -5706,19 +5670,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>83.3</v>
+        <v>96.7</v>
       </c>
       <c r="G3" s="2">
-        <v>16.7</v>
+        <v>3.3</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5729,7 +5693,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5738,16 +5702,16 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>8.1</v>
@@ -5761,7 +5725,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -5770,19 +5734,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5793,7 +5757,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -5802,19 +5766,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5825,7 +5789,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -5846,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5878,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5928,7 +5892,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5966,16 +5930,16 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5983,19 +5947,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920001</v>
+        <v>21330051920167</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" t="s">
         <v>73</v>
       </c>
-      <c r="D3" t="s">
-        <v>80</v>
-      </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>56</v>
@@ -6006,231 +5970,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920167</v>
+        <v>20330051920069</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" t="s">
         <v>74</v>
       </c>
-      <c r="D4" t="s">
-        <v>81</v>
-      </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920167</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920169</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920169</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920176</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920176</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920069</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920069</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920153</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920166</v>
-      </c>
-      <c r="B13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEM - Estadisticos 20231.xlsx
+++ b/grupos/5AEM - Estadisticos 20231.xlsx
@@ -811,25 +811,25 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z4">
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -900,25 +900,25 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -992,13 +992,13 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA6">
         <v>10</v>
@@ -1007,7 +1007,7 @@
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1078,25 +1078,25 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1167,25 +1167,25 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB8">
         <v>10</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1256,25 +1256,25 @@
         <v>10</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB9">
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1345,25 +1345,25 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1434,25 +1434,25 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1523,25 +1523,25 @@
         <v>3</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1612,25 +1612,25 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB13">
         <v>10</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1701,25 +1701,25 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1790,25 +1790,25 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1879,25 +1879,25 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1968,25 +1968,25 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2057,25 +2057,25 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2149,22 +2149,22 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2235,25 +2235,25 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2324,25 +2324,25 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA21">
         <v>10</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2413,25 +2413,25 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2502,25 +2502,25 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB23">
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2591,25 +2591,25 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2680,22 +2680,22 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>10</v>
@@ -2769,25 +2769,25 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2858,22 +2858,22 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC27">
         <v>10</v>
@@ -2947,25 +2947,25 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3036,25 +3036,25 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3125,25 +3125,25 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z30">
         <v>5</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3214,25 +3214,25 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA31">
         <v>10</v>
       </c>
       <c r="AB31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC31">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3303,25 +3303,25 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3395,13 +3395,13 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA33">
         <v>10</v>
@@ -3410,7 +3410,7 @@
         <v>10</v>
       </c>
       <c r="AC33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5650,7 +5650,7 @@
         <v>6.7</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5682,7 +5682,7 @@
         <v>3.3</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5746,7 +5746,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5778,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5810,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/5AEM - Estadisticos 20231.xlsx
+++ b/grupos/5AEM - Estadisticos 20231.xlsx
@@ -811,25 +811,25 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -900,25 +900,25 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -992,13 +992,13 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>10</v>
@@ -1007,7 +1007,7 @@
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1078,25 +1078,25 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1167,25 +1167,25 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB8">
         <v>10</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1256,25 +1256,25 @@
         <v>10</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1345,25 +1345,25 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1434,25 +1434,25 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1523,25 +1523,25 @@
         <v>3</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1612,25 +1612,25 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>10</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1701,25 +1701,25 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1790,25 +1790,25 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1879,25 +1879,25 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1968,25 +1968,25 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2057,25 +2057,25 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2149,22 +2149,22 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2235,25 +2235,25 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2324,25 +2324,25 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>10</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2413,25 +2413,25 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2502,25 +2502,25 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2591,25 +2591,25 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2680,22 +2680,22 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>10</v>
@@ -2769,25 +2769,25 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2858,22 +2858,22 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>10</v>
@@ -2947,25 +2947,25 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3036,25 +3036,25 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3125,25 +3125,25 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>5</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3214,25 +3214,25 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>10</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3303,25 +3303,25 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3395,13 +3395,13 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA33">
         <v>10</v>
@@ -3410,7 +3410,7 @@
         <v>10</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -5650,7 +5650,7 @@
         <v>6.7</v>
       </c>
       <c r="H2">
-        <v>9.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5682,7 +5682,7 @@
         <v>3.3</v>
       </c>
       <c r="H3">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5746,7 +5746,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5778,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5810,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="I8">
         <v>0</v>
